--- a/01_[머신러닝_회귀&군집]_소규모_주점의_일매출_예측과_영업일_유형화/cat_summary.xlsx
+++ b/01_[머신러닝_회귀&군집]_소규모_주점의_일매출_예측과_영업일_유형화/cat_summary.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
@@ -25,10 +24,18 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
@@ -45,12 +52,27 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -63,14 +85,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -582,13 +607,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>708</v>
+        <v>702</v>
       </c>
       <c r="C5" t="n">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="D5" t="n">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="E5" t="n">
         <v>105</v>
@@ -597,7 +622,7 @@
         <v>184</v>
       </c>
       <c r="G5" t="n">
-        <v>707</v>
+        <v>688</v>
       </c>
       <c r="H5" t="n">
         <v>431</v>
@@ -607,7 +632,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -621,42 +646,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>휴무여부</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>ratio</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>708</v>
+        <v>702</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9698630136986301</v>
+        <v>0.9616438356164384</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C3" t="n">
-        <v>0.03013698630136986</v>
+        <v>0.03835616438356165</v>
       </c>
     </row>
   </sheetData>
@@ -674,42 +699,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>공휴일여부</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>ratio</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="C2" t="n">
-        <v>0.952054794520548</v>
+        <v>0.947945205479452</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C3" t="n">
-        <v>0.04794520547945205</v>
+        <v>0.05205479452054795</v>
       </c>
     </row>
   </sheetData>
@@ -727,42 +752,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>공휴일전날여부</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>ratio</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="C2" t="n">
-        <v>0.952054794520548</v>
+        <v>0.947945205479452</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C3" t="n">
-        <v>0.04794520547945205</v>
+        <v>0.05205479452054795</v>
       </c>
     </row>
   </sheetData>
@@ -780,24 +805,24 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>요일</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>ratio</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
@@ -810,7 +835,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
@@ -823,7 +848,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
@@ -836,7 +861,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
@@ -849,7 +874,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
@@ -862,7 +887,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
@@ -875,7 +900,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
@@ -902,24 +927,24 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>계절</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>ratio</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>봄</t>
         </is>
@@ -932,7 +957,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>여름</t>
         </is>
@@ -945,7 +970,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>가을</t>
         </is>
@@ -958,7 +983,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>겨울</t>
         </is>
@@ -985,42 +1010,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>연휴여부</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>ratio</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>707</v>
+        <v>688</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9684931506849315</v>
+        <v>0.9424657534246575</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0315068493150685</v>
+        <v>0.05753424657534247</v>
       </c>
     </row>
   </sheetData>
@@ -1038,24 +1063,24 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>광고_실시여부</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>ratio</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="B2" t="n">
@@ -1066,7 +1091,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="B3" t="n">
@@ -1091,24 +1116,24 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>기상특보여부</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>ratio</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="B2" t="n">
@@ -1119,7 +1144,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>1</v>
       </c>
       <c r="B3" t="n">
